--- a/artfynd/A 5100-2023 artfynd.xlsx
+++ b/artfynd/A 5100-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5100-2023 artfynd.xlsx
+++ b/artfynd/A 5100-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96010845</v>
+        <v>110095550</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Åssved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483447.5113221028</v>
+        <v>483551</v>
       </c>
       <c r="R2" t="n">
-        <v>6999152.421467176</v>
+        <v>6999206</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,27 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,52 +783,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96010985</v>
+        <v>110095680</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Åssved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483535.0724740143</v>
+        <v>483496</v>
       </c>
       <c r="R3" t="n">
-        <v>6999262.386826213</v>
+        <v>6999265</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,52 +891,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96010901</v>
+        <v>110095772</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Åssved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483480.8686257744</v>
+        <v>483487</v>
       </c>
       <c r="R4" t="n">
-        <v>6999207.004943795</v>
+        <v>6999238</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,22 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,52 +999,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96010814</v>
+        <v>110096308</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Åssved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483448.4383765963</v>
+        <v>483447</v>
       </c>
       <c r="R5" t="n">
-        <v>6999156.489353669</v>
+        <v>6999150</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,22 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,52 +1107,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96010960</v>
+        <v>110096681</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Åssved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483530.0468614629</v>
+        <v>483513</v>
       </c>
       <c r="R6" t="n">
-        <v>6999254.267387364</v>
+        <v>6999108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,22 +1173,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96010941</v>
+        <v>110095624</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,16 +1226,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1285,17 +1245,16 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Åssved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483501.1376121418</v>
+        <v>483502</v>
       </c>
       <c r="R7" t="n">
-        <v>6999272.061907188</v>
+        <v>6999281</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,22 +1281,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,51 +1323,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110095680</v>
+        <v>96010738</v>
       </c>
       <c r="B8" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483496.1165388314</v>
+        <v>483449</v>
       </c>
       <c r="R8" t="n">
-        <v>6999264.847517633</v>
+        <v>6999122</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1435,22 +1390,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,15 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110095631</v>
+        <v>96010814</v>
       </c>
       <c r="B9" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,16 +1452,17 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483502.0899105198</v>
+        <v>483449</v>
       </c>
       <c r="R9" t="n">
-        <v>6999281.10698786</v>
+        <v>6999156</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,22 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,51 +1521,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110095772</v>
+        <v>96010845</v>
       </c>
       <c r="B10" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483487.3690896929</v>
+        <v>483448</v>
       </c>
       <c r="R10" t="n">
-        <v>6999237.742085094</v>
+        <v>6999152</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,22 +1588,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,51 +1625,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110096681</v>
+        <v>96010867</v>
       </c>
       <c r="B11" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483512.9911666384</v>
+        <v>483447</v>
       </c>
       <c r="R11" t="n">
-        <v>6999108.193482363</v>
+        <v>6999146</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1774,22 +1692,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,15 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110095692</v>
+        <v>96010901</v>
       </c>
       <c r="B12" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,16 +1754,17 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483496.1165388314</v>
+        <v>483481</v>
       </c>
       <c r="R12" t="n">
-        <v>6999264.847517633</v>
+        <v>6999207</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1887,22 +1791,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,15 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110095624</v>
+        <v>96010941</v>
       </c>
       <c r="B13" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,16 +1834,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1964,16 +1853,17 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483502.0899105198</v>
+        <v>483501</v>
       </c>
       <c r="R13" t="n">
-        <v>6999281.10698786</v>
+        <v>6999272</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2000,22 +1890,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,15 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110095597</v>
+        <v>96010960</v>
       </c>
       <c r="B14" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,16 +1952,17 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483532.2871190881</v>
+        <v>483530</v>
       </c>
       <c r="R14" t="n">
-        <v>6999249.278501262</v>
+        <v>6999254</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,22 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,15 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110096397</v>
+        <v>96010985</v>
       </c>
       <c r="B15" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,16 +2051,17 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483470.9237994384</v>
+        <v>483535</v>
       </c>
       <c r="R15" t="n">
-        <v>6999122.888413358</v>
+        <v>6999262</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,22 +2088,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,15 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110096029</v>
+        <v>96011349</v>
       </c>
       <c r="B16" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,16 +2150,17 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åssved, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483432.16984496</v>
+        <v>483568</v>
       </c>
       <c r="R16" t="n">
-        <v>6999165.170241018</v>
+        <v>6999231</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2339,22 +2187,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,15 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110131142</v>
+        <v>110095495</v>
       </c>
       <c r="B17" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483415.7647517173</v>
+        <v>483557</v>
       </c>
       <c r="R17" t="n">
-        <v>6999147.153631656</v>
+        <v>6999208</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2452,22 +2285,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,6 +2324,1194 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110095559</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>483550</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6999212</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110095597</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483532</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6999249</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110095631</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>483502</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6999281</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>110095692</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>483496</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6999265</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>110095989</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>483444</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6999137</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110096004</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>483411</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6999148</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>110096029</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>483432</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6999166</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>110096397</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>483470</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6999122</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>110096716</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>483556</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6999105</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110131142</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>483415</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6999147</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>110133274</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Åssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>483555</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6999227</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5100-2023 artfynd.xlsx
+++ b/artfynd/A 5100-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095550</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095772</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110096308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110096681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095624</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010738</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010814</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010845</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1721,6 +1771,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010867</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010901</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010941</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010960</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96010985</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96011349</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095495</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2432,6 +2517,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095559</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2540,6 +2630,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095597</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2648,6 +2743,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095631</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2756,6 +2856,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095692</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2864,6 +2969,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110095989</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2972,6 +3082,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110096004</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3080,6 +3195,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110096029</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3188,6 +3308,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110096397</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3296,6 +3421,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110096716</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3404,6 +3534,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110131142</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3512,8 +3647,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110133274</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>